--- a/tame_output/ON/bt/strategyON_20240314.xlsx
+++ b/tame_output/ON/bt/strategyON_20240314.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-268.5%</t>
+          <t>-268.3%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-104.3%</t>
+          <t>-104.1%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-68.1%</t>
+          <t>-67.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-37.5%</t>
         </is>
       </c>
     </row>
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-1.069687941111592</v>
+        <v>-1.066843671534732</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.719701638244056</v>
+        <v>2.720839346074799</v>
       </c>
       <c r="F1902" t="n">
-        <v>1.559175623742219</v>
+        <v>1.562019893319079</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.083438613247771</v>
+        <v>4.085145174993887</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240314.xlsx
+++ b/tame_output/ON/bt/strategyON_20240314.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,27 +1007,27 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>465.4%</t>
+          <t>464.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-268.3%</t>
+          <t>-293.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-104.1%</t>
+          <t>-114.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,27 +1323,27 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-67.8%</t>
+          <t>-93.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-52.9%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-1.066843671534732</v>
+        <v>-1.323614617218895</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.720839346074799</v>
+        <v>2.618130967801134</v>
       </c>
       <c r="F1902" t="n">
-        <v>1.562019893319079</v>
+        <v>1.305248947634916</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.085145174993887</v>
+        <v>3.931082607583389</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240314.xlsx
+++ b/tame_output/ON/bt/strategyON_20240314.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-55.0%</t>
+          <t>-53.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>105.2%</t>
+          <t>105.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-46.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>463.8%</t>
+          <t>464.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-322.3%</t>
+          <t>-299.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-125.7%</t>
+          <t>-116.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-228.9%</t>
+          <t>-210.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-121.8%</t>
+          <t>-99.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-6.152593093700998</v>
+        <v>-6.182802820589554</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.6674779263991168</v>
+        <v>0.6553940356436945</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9094140384302598</v>
+        <v>-0.9396237653188155</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.583223165135108</v>
+        <v>2.565097329001975</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-6.146116946907439</v>
+        <v>-6.176326673795995</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.6731101357383094</v>
+        <v>0.6610262449828874</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9029378916367002</v>
+        <v>-0.933147618525256</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.590150603833012</v>
+        <v>2.572024767699879</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-6.142426021951027</v>
+        <v>-6.172635748839583</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.6745865057208742</v>
+        <v>0.6625026149654518</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9029378916367002</v>
+        <v>-0.933147618525256</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.590150603833012</v>
+        <v>2.572024767699879</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-6.135210669079211</v>
+        <v>-6.165420395967767</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.6829858439882428</v>
+        <v>0.6709019532328204</v>
       </c>
       <c r="F1878" t="n">
-        <v>-0.8331596563463184</v>
+        <v>-0.8633693832348741</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.637530742125884</v>
+        <v>2.61940490599275</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.084182822997385</v>
+        <v>-6.114392549885941</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.7078795369054096</v>
+        <v>0.6957956461499872</v>
       </c>
       <c r="F1879" t="n">
-        <v>-0.7579503180392174</v>
+        <v>-0.7881600449277731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.687138899594581</v>
+        <v>2.669013063461447</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.010712991329937</v>
+        <v>-6.040922718218493</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.7526391710658098</v>
+        <v>0.7405552803103874</v>
       </c>
       <c r="F1880" t="n">
-        <v>-0.6844804863717691</v>
+        <v>-0.7146902132603248</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.746592500088471</v>
+        <v>2.728466663955337</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-5.930340635866007</v>
+        <v>-5.960550362754563</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.7993433339988987</v>
+        <v>0.7872594432434763</v>
       </c>
       <c r="F1881" t="n">
-        <v>-0.6041081309078394</v>
+        <v>-0.6343178577963952</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.809371134114345</v>
+        <v>2.791245297981212</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-5.897408766053156</v>
+        <v>-5.927618492941712</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.8052969170224431</v>
+        <v>0.7932130262670207</v>
       </c>
       <c r="F1882" t="n">
-        <v>-0.6041081309078394</v>
+        <v>-0.6343178577963952</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.802151969212749</v>
+        <v>2.784026133079616</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-5.917573407602704</v>
+        <v>-5.947783134491259</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.7905588696286481</v>
+        <v>0.7784749788732257</v>
       </c>
       <c r="F1883" t="n">
-        <v>-0.6242727724573868</v>
+        <v>-0.6544824993459425</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.783380993509045</v>
+        <v>2.765255157375911</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-5.85890647758117</v>
+        <v>-5.889116204469726</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.8151414314758174</v>
+        <v>0.803057540720395</v>
       </c>
       <c r="F1884" t="n">
-        <v>-0.5393133040272491</v>
+        <v>-0.5695230309158048</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.835472464405684</v>
+        <v>2.81734662827255</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-5.79583724527483</v>
+        <v>-5.826046972163386</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.843062853027468</v>
+        <v>0.830978962272046</v>
       </c>
       <c r="F1885" t="n">
-        <v>-0.5678268667094836</v>
+        <v>-0.5980365935980393</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.821058055425458</v>
+        <v>2.802932219292324</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-5.743821731306018</v>
+        <v>-5.774031458194574</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.8678593943013939</v>
+        <v>0.8557755035459715</v>
       </c>
       <c r="F1886" t="n">
-        <v>-0.5678268667094836</v>
+        <v>-0.5980365935980393</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.825048391111859</v>
+        <v>2.806922554978725</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-5.568252062385114</v>
+        <v>-5.59846178927367</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.9366120349710139</v>
+        <v>0.9245281442155915</v>
       </c>
       <c r="F1887" t="n">
-        <v>-0.5678268667094836</v>
+        <v>-0.5980365935980393</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.823573164213117</v>
+        <v>2.805447328079984</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-5.370982656657116</v>
+        <v>-5.401192383545672</v>
       </c>
       <c r="E1888" t="n">
-        <v>1.030573207427085</v>
+        <v>1.018489316671663</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.3705574609814855</v>
+        <v>-0.4007671878700412</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.956988217814788</v>
+        <v>2.938862381681655</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-5.171830549420017</v>
+        <v>-5.202040276308573</v>
       </c>
       <c r="E1889" t="n">
-        <v>1.097182916675242</v>
+        <v>1.08509902591982</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.2052349350316721</v>
+        <v>-0.2354446619202278</v>
       </c>
       <c r="G1889" t="n">
-        <v>3.043130599737993</v>
+        <v>3.025004763604859</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-4.945985396700606</v>
+        <v>-4.976195123589162</v>
       </c>
       <c r="E1890" t="n">
-        <v>1.197100050799215</v>
+        <v>1.185016160043793</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.1633082594445084</v>
+        <v>-0.1935179863330642</v>
       </c>
       <c r="G1890" t="n">
-        <v>3.0778656781265</v>
+        <v>3.059739841993367</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-4.659710584377912</v>
+        <v>-4.689920311266468</v>
       </c>
       <c r="E1891" t="n">
-        <v>1.312749120284352</v>
+        <v>1.300665229528929</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.1633082594445084</v>
+        <v>-0.1935179863330642</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.079004822682559</v>
+        <v>3.060878986549425</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-4.432914757304578</v>
+        <v>-4.463124484193134</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.406101225275793</v>
+        <v>1.39401733452037</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.09519431482296392</v>
+        <v>-0.1254040417115196</v>
       </c>
       <c r="G1892" t="n">
-        <v>3.122506963617593</v>
+        <v>3.104381127484459</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.149006026375829</v>
+        <v>-4.179215753264385</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.525398421885929</v>
+        <v>1.513314531130506</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.09519431482296392</v>
+        <v>-0.1254040417115196</v>
       </c>
       <c r="G1893" t="n">
-        <v>3.12824066785623</v>
+        <v>3.110114831723096</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-3.902018776182878</v>
+        <v>-3.932228503071433</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.614456059569244</v>
+        <v>1.602372168813822</v>
       </c>
       <c r="F1894" t="n">
-        <v>0.1517929353699882</v>
+        <v>0.1215832084814324</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.266695755578136</v>
+        <v>3.248569919445002</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-3.638181908978809</v>
+        <v>-3.668391635867364</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.710107325137964</v>
+        <v>1.698023434382542</v>
       </c>
       <c r="F1895" t="n">
-        <v>0.1517929353699882</v>
+        <v>0.1215832084814324</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.256812274265228</v>
+        <v>3.238686438132095</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-3.370940108110411</v>
+        <v>-3.401149834998967</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.815169484985949</v>
+        <v>1.803085594230527</v>
       </c>
       <c r="F1896" t="n">
-        <v>0.1517929353699882</v>
+        <v>0.1215832084814324</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.254977713765854</v>
+        <v>3.236851877632721</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-3.095130944709927</v>
+        <v>-3.125340671598483</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.925192835372682</v>
+        <v>1.91310894461726</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.2408122436487217</v>
+        <v>0.2106025167601659</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.308088983759633</v>
+        <v>3.2899631476265</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-2.826063356942948</v>
+        <v>-2.856273083831504</v>
       </c>
       <c r="E1898" t="n">
-        <v>2.033488376624968</v>
+        <v>2.021404485869545</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.509879831415701</v>
+        <v>0.4796701045271453</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.470198042565315</v>
+        <v>3.452072206432181</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-2.562003418620152</v>
+        <v>-2.592213145508707</v>
       </c>
       <c r="E1899" t="n">
-        <v>2.125852035792334</v>
+        <v>2.113768145036912</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.7739397697384972</v>
+        <v>0.7437300428499415</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.615373689397241</v>
+        <v>3.597247853264107</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-1.854923795115314</v>
+        <v>-1.88513352200387</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.405896851533968</v>
+        <v>2.393812960778546</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.7739397697384972</v>
+        <v>0.7437300428499415</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.61258665573694</v>
+        <v>3.594460819603806</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-1.605282765129362</v>
+        <v>-1.635492492017918</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.50609688741619</v>
+        <v>2.494012996660768</v>
       </c>
       <c r="F1901" t="n">
-        <v>1.023580799724449</v>
+        <v>0.9933710728358931</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.762714897616352</v>
+        <v>3.744589061483218</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-1.606835576210254</v>
+        <v>-1.380950592676842</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.50484258420459</v>
+        <v>2.595196577617955</v>
       </c>
       <c r="F1902" t="n">
-        <v>1.022027988643557</v>
+        <v>1.247912972176969</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.761150032188574</v>
+        <v>3.896681022308621</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,19 +45314,19 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.564252589030636</v>
+        <v>3.564252589030635</v>
       </c>
       <c r="C1903" t="n">
         <v>2.916329177957524</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.606835576210254</v>
+        <v>-1.380950592676842</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.50484258420459</v>
+        <v>2.595196577617955</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.022027988643557</v>
+        <v>1.247912972176969</v>
       </c>
       <c r="G1903" t="n">
         <v>2.909392974943892</v>

--- a/tame_output/ON/bt/strategyON_20240314.xlsx
+++ b/tame_output/ON/bt/strategyON_20240314.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-51.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>105.6%</t>
+          <t>105.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-43.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>464.8%</t>
+          <t>465.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-299.7%</t>
+          <t>-277.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-116.7%</t>
+          <t>-107.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,27 +1323,27 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-99.2%</t>
+          <t>-77.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,52 +1456,52 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-42.4%</t>
         </is>
       </c>
     </row>
@@ -45317,19 +45317,19 @@
         <v>3.564252589030635</v>
       </c>
       <c r="C1903" t="n">
-        <v>2.916329177957524</v>
+        <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.380950592676842</v>
+        <v>-1.161761261593004</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.595196577617955</v>
+        <v>2.690796738889343</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.247912972176969</v>
+        <v>1.467102303260807</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.909392974943892</v>
+        <v>4.036119049796776</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240314.xlsx
+++ b/tame_output/ON/bt/strategyON_20240314.xlsx
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.2%</t>
         </is>
       </c>
     </row>
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.161761261593004</v>
+        <v>-1.161120176507329</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.690796738889343</v>
+        <v>2.691053172923613</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.467102303260807</v>
+        <v>1.467743388346482</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.036119049796776</v>
+        <v>4.036503700848181</v>
       </c>
     </row>
   </sheetData>
